--- a/Task 2/ECG_Features_Data.xlsx
+++ b/Task 2/ECG_Features_Data.xlsx
@@ -413,58 +413,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Signal_Name</t>
+          <t>signalName</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>R_Peak_Index</t>
+          <t>rPeakIndex</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>QR_Interval_s</t>
+          <t>qrInterval</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>RS_Interval_s</t>
+          <t>rsInterval</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>QS_Slope</t>
+          <t>qsSlope</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>DWT_Energy_cA3</t>
+          <t>dwtMean</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>DWT_Energy_cD3</t>
+          <t>dwtStd</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AC_DCT_1</t>
+          <t>dwtEnergy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>AC_DCT_2</t>
+          <t>acDctPos_1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>AC_DCT_3</t>
+          <t>acDctPos_2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>acDctPos_3</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>acDctPos_4</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>acDctPos_5</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>acDctPos_6</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>acDctPos_7</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>acDctPos_8</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>acDctPos_9</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>acDctPos_10</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>acDctPos_11</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>acDctPos_12</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>acDctPos_13</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>acDctPos_14</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>acDctPos_15</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>acDctPos_16</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>acDctPos_17</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>acDctPos_18</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>acDctPos_19</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>acDctPos_20</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>acDctPos_21</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>acDctPos_22</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>acDctPos_23</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>acDctPos_24</t>
         </is>
       </c>
     </row>
@@ -478,28 +588,94 @@
         <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>0.024</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.028</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1799.698980458059</v>
+        <v>7.198795921832234</v>
       </c>
       <c r="F2" t="n">
-        <v>4938346.176444116</v>
+        <v>67.75133795666832</v>
       </c>
       <c r="G2" t="n">
-        <v>2528733.710786351</v>
+        <v>490.1500319914041</v>
       </c>
       <c r="H2" t="n">
+        <v>6855444.334370608</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.000000000000001</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2.491970842333611</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1.164327569053433</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.299841672054215</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12.87004323702244</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11.77148176866267</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.944493877122107</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.793368830434655</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11.18779330347075</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.160598579951996</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.523387853108882</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.053109861936131</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.189548120011074</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.781983006577956</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.864857889048514</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.257865475026338</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.891713029787216</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.351401948105614</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2981493716293189</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.966253287048161</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.175467723296918</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.1777561126143999</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2715028033205235</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1350321484290938</v>
       </c>
     </row>
     <row r="3">
@@ -512,28 +688,94 @@
         <v>132</v>
       </c>
       <c r="C3" t="n">
-        <v>0.024</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.024</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1779.2176198594</v>
+        <v>7.116870479437599</v>
       </c>
       <c r="F3" t="n">
-        <v>4083762.301506432</v>
+        <v>32.64234497148087</v>
       </c>
       <c r="G3" t="n">
-        <v>3217678.770959348</v>
+        <v>480.3427831002286</v>
       </c>
       <c r="H3" t="n">
+        <v>6953841.358851315</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.000000000000001</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>4.349703069362203</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1.947926390755595</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.1289875425455</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8.529422428350358</v>
+      </c>
+      <c r="N3" t="n">
+        <v>11.83274280604073</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7.975959538615813</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.992833131656384</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.320656742926698</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.928843377860389</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6.121895140489875</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.256554898108472</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.19490482411358</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.328123209041539</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.646513529500785</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.023423674005268</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.1000628776852</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.059300340879212</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.733039116648336</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.47747925564975</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.496269852163348</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.758526759055941</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.223933423377107</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.4003542568609212</v>
       </c>
     </row>
   </sheetData>
